--- a/CallCenter_Arcoiris/Dashboard_Performance_CallCenter_Arcoiris.xlsx
+++ b/CallCenter_Arcoiris/Dashboard_Performance_CallCenter_Arcoiris.xlsx
@@ -586,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -689,7 +689,12 @@
     <xf borderId="7" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="12" numFmtId="2" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="6" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="12" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1085,11 +1090,11 @@
           </c:val>
         </c:ser>
         <c:overlap val="100"/>
-        <c:axId val="1009829643"/>
-        <c:axId val="1452301231"/>
+        <c:axId val="1763970541"/>
+        <c:axId val="690308085"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1009829643"/>
+        <c:axId val="1763970541"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1141,10 +1146,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1452301231"/>
+        <c:crossAx val="690308085"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1452301231"/>
+        <c:axId val="690308085"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1219,7 +1224,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1009829643"/>
+        <c:crossAx val="1763970541"/>
         <c:crosses val="max"/>
       </c:valAx>
     </c:plotArea>
@@ -1297,11 +1302,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1745625343"/>
-        <c:axId val="60976610"/>
+        <c:axId val="212148872"/>
+        <c:axId val="285681307"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1745625343"/>
+        <c:axId val="212148872"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1353,10 +1358,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60976610"/>
+        <c:crossAx val="285681307"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60976610"/>
+        <c:axId val="285681307"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1431,7 +1436,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1745625343"/>
+        <c:crossAx val="212148872"/>
         <c:crosses val="max"/>
       </c:valAx>
     </c:plotArea>
@@ -1844,11 +1849,11 @@
           </c:val>
         </c:ser>
         <c:overlap val="100"/>
-        <c:axId val="1631838425"/>
-        <c:axId val="219406855"/>
+        <c:axId val="1397116283"/>
+        <c:axId val="1077941899"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1631838425"/>
+        <c:axId val="1397116283"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1900,10 +1905,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="219406855"/>
+        <c:crossAx val="1077941899"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="219406855"/>
+        <c:axId val="1077941899"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1978,7 +1983,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1631838425"/>
+        <c:crossAx val="1397116283"/>
         <c:crosses val="max"/>
       </c:valAx>
     </c:plotArea>
@@ -30539,7 +30544,7 @@
       <c r="B55" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="C55" s="47" t="s">
+      <c r="C55" s="48" t="s">
         <v>71</v>
       </c>
       <c r="N55" s="42"/>
@@ -30549,7 +30554,7 @@
       <c r="B56" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="C56" s="48">
+      <c r="C56" s="49">
         <v>5.575</v>
       </c>
       <c r="N56" s="42"/>
@@ -30559,7 +30564,7 @@
       <c r="B57" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="C57" s="48">
+      <c r="C57" s="49">
         <v>5.55</v>
       </c>
       <c r="N57" s="42"/>
@@ -30569,7 +30574,7 @@
       <c r="B58" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="48">
+      <c r="C58" s="49">
         <v>5.550000000000001</v>
       </c>
       <c r="N58" s="42"/>
@@ -30579,7 +30584,7 @@
       <c r="B59" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="C59" s="48">
+      <c r="C59" s="49">
         <v>5.516666666666667</v>
       </c>
       <c r="N59" s="42"/>
@@ -30589,7 +30594,7 @@
       <c r="B60" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="48">
+      <c r="C60" s="49">
         <v>5.508333333333333</v>
       </c>
       <c r="N60" s="42"/>
@@ -30599,7 +30604,7 @@
       <c r="B61" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="C61" s="48">
+      <c r="C61" s="49">
         <v>5.474999999999999</v>
       </c>
       <c r="N61" s="42"/>
@@ -30609,7 +30614,7 @@
       <c r="B62" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="48">
+      <c r="C62" s="49">
         <v>5.408333333333332</v>
       </c>
       <c r="N62" s="42"/>
@@ -30619,7 +30624,7 @@
       <c r="B63" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C63" s="48">
+      <c r="C63" s="49">
         <v>5.383333333333333</v>
       </c>
       <c r="N63" s="42"/>
@@ -30629,7 +30634,7 @@
       <c r="B64" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="C64" s="48">
+      <c r="C64" s="49">
         <v>5.325</v>
       </c>
       <c r="N64" s="42"/>
@@ -30639,7 +30644,7 @@
       <c r="B65" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="48">
+      <c r="C65" s="49">
         <v>4.633333333333334</v>
       </c>
       <c r="N65" s="42"/>
@@ -30689,20 +30694,20 @@
       <c r="N76" s="24"/>
     </row>
     <row r="77">
-      <c r="A77" s="49"/>
-      <c r="B77" s="50"/>
-      <c r="C77" s="50"/>
-      <c r="D77" s="50"/>
-      <c r="E77" s="50"/>
-      <c r="F77" s="50"/>
-      <c r="G77" s="50"/>
-      <c r="H77" s="50"/>
-      <c r="I77" s="50"/>
-      <c r="J77" s="50"/>
-      <c r="K77" s="50"/>
-      <c r="L77" s="50"/>
-      <c r="M77" s="50"/>
-      <c r="N77" s="51"/>
+      <c r="A77" s="50"/>
+      <c r="B77" s="51"/>
+      <c r="C77" s="51"/>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
+      <c r="F77" s="51"/>
+      <c r="G77" s="51"/>
+      <c r="H77" s="51"/>
+      <c r="I77" s="51"/>
+      <c r="J77" s="51"/>
+      <c r="K77" s="51"/>
+      <c r="L77" s="51"/>
+      <c r="M77" s="51"/>
+      <c r="N77" s="52"/>
     </row>
     <row r="78">
       <c r="A78" s="23"/>
@@ -30734,194 +30739,194 @@
   <sheetData>
     <row r="1" ht="225.0" customHeight="1"/>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="H3" s="52" t="s">
+      <c r="H3" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="52" t="s">
+      <c r="I3" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="J3" s="52" t="s">
+      <c r="J3" s="53" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54">
+      <c r="B4" s="54"/>
+      <c r="C4" s="55">
         <v>178.0</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="54">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="55">
         <v>195.0</v>
       </c>
-      <c r="J5" s="53"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="54">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="55">
         <v>194.0</v>
       </c>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="54">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="55">
         <v>189.0</v>
       </c>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="54">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55">
         <v>194.0</v>
       </c>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="54">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="55">
         <v>181.0</v>
       </c>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="54">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="55">
         <v>190.0</v>
       </c>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="54">
+      <c r="B11" s="55">
         <v>177.0</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="54">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="55">
         <v>182.0</v>
       </c>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="54">
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="55">
         <v>203.0</v>
       </c>
     </row>
